--- a/metrics/qualitative_assesment/qualitative_ranking_per_dataset.xlsx
+++ b/metrics/qualitative_assesment/qualitative_ranking_per_dataset.xlsx
@@ -104,10 +104,10 @@
     <t xml:space="preserve">Highlighted cells indicate the top-ranked (1st place) model(s) for that dataset, including ties.</t>
   </si>
   <si>
-    <t xml:space="preserve">LLaMA-3-70B-4bits ranks first (outright or tied) in all six datasets, indicating consistent leadership rather than a result driven by a single dataset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPT-4 and GPT-4o tie for first place in three of the six datasets (Airlines, Amazon, Brazilian) but are not the top-ranked model in BigBasket, Customer, or Ecommerce.</t>
+    <t xml:space="preserve">LLaMA-3-70B-4bits ranks first (outright or tied) in five of the six datasets (all except Brazilian), indicating that its top aggregate position largely reflects consistent leadership rather than a result driven by a single dataset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-4 ranks first (outright or tied) in three of the six datasets (Airlines, Amazon, Brazilian) and GPT-4o in two (Amazon, Brazilian); neither is the top-ranked model in BigBasket, Customer, or Ecommerce.</t>
   </si>
   <si>
     <t xml:space="preserve">Qualitative Evaluation — Per-Dataset Ranking Scores (Fine-tuned Models)</t>
@@ -270,16 +270,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -311,7 +315,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -570,539 +574,539 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="8" t="n">
+      <c r="B5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="9" t="n">
         <f aca="false">SUM(B5:G5)</f>
         <v>25</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <f aca="false">RANK(H5,$H$5:$H$18)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="8" t="n">
+      <c r="B6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="9" t="n">
         <f aca="false">SUM(B6:G6)</f>
         <v>25</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <f aca="false">RANK(H6,$H$5:$H$18)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="7" t="n">
+      <c r="B7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <f aca="false">SUM(B7:G7)</f>
         <v>13.5</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <f aca="false">RANK(H7,$H$5:$H$18)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="8" t="n">
+      <c r="B8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="9" t="n">
         <f aca="false">SUM(B8:G8)</f>
         <v>29</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <f aca="false">RANK(H8,$H$5:$H$18)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="B9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="n">
         <f aca="false">SUM(B9:G9)</f>
         <v>12</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10" t="n">
         <f aca="false">RANK(H9,$H$5:$H$18)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="n">
+      <c r="B10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="E10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="9" t="n">
         <f aca="false">SUM(B10:G10)</f>
         <v>6.5</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10" t="n">
         <f aca="false">RANK(H10,$H$5:$H$18)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="B11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="9" t="n">
         <f aca="false">SUM(B11:G11)</f>
         <v>19</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="10" t="n">
         <f aca="false">RANK(H11,$H$5:$H$18)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="B12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="9" t="n">
         <f aca="false">SUM(B12:G12)</f>
         <v>21</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="10" t="n">
         <f aca="false">RANK(H12,$H$5:$H$18)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="B13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9" t="n">
         <f aca="false">SUM(B13:G13)</f>
         <v>17</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <f aca="false">RANK(H13,$H$5:$H$18)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="B14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="n">
         <f aca="false">SUM(B14:G14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="10" t="n">
         <f aca="false">RANK(H14,$H$5:$H$18)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="7" t="n">
+      <c r="B15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="F15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="9" t="n">
         <f aca="false">SUM(B15:G15)</f>
         <v>7.5</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="10" t="n">
         <f aca="false">RANK(H15,$H$5:$H$18)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="B16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="9" t="n">
         <f aca="false">SUM(B16:G16)</f>
         <v>6</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="10" t="n">
         <f aca="false">RANK(H16,$H$5:$H$18)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8" t="n">
+      <c r="B17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9" t="n">
         <f aca="false">SUM(B17:G17)</f>
         <v>10</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10" t="n">
         <f aca="false">RANK(H17,$H$5:$H$18)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8" t="n">
+      <c r="B18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9" t="n">
         <f aca="false">SUM(B18:G18)</f>
         <v>1</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="10" t="n">
         <f aca="false">RANK(H18,$H$5:$H$18)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1130,403 +1134,403 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="8" t="n">
+      <c r="B5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="9" t="n">
         <f aca="false">SUM(B5:G5)</f>
         <v>25</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <f aca="false">RANK(H5,$H$5:$H$14)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="8" t="n">
+      <c r="B6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="9" t="n">
         <f aca="false">SUM(B6:G6)</f>
         <v>19</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <f aca="false">RANK(H6,$H$5:$H$14)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="8" t="n">
+      <c r="B7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="9" t="n">
         <f aca="false">SUM(B7:G7)</f>
         <v>18</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <f aca="false">RANK(H7,$H$5:$H$14)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="8" t="n">
+      <c r="B8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="9" t="n">
         <f aca="false">SUM(B8:G8)</f>
         <v>19</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <f aca="false">RANK(H8,$H$5:$H$14)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="B9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="9" t="n">
         <f aca="false">SUM(B9:G9)</f>
         <v>19</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10" t="n">
         <f aca="false">RANK(H9,$H$5:$H$14)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="7" t="n">
+      <c r="B10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="F10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="9" t="n">
         <f aca="false">SUM(B10:G10)</f>
         <v>14.5</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10" t="n">
         <f aca="false">RANK(H10,$H$5:$H$14)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="B11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="9" t="n">
         <f aca="false">SUM(B11:G11)</f>
         <v>19</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="10" t="n">
         <f aca="false">RANK(H11,$H$5:$H$14)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="7" t="n">
+      <c r="B12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="F12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="n">
         <f aca="false">SUM(B12:G12)</f>
         <v>13.5</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="10" t="n">
         <f aca="false">RANK(H12,$H$5:$H$14)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="7" t="n">
+      <c r="B13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="7" t="n">
+      <c r="D13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="7" t="n">
+      <c r="F13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <f aca="false">SUM(B13:G13)</f>
         <v>11.5</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <f aca="false">RANK(H13,$H$5:$H$14)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="B14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="n">
         <f aca="false">SUM(B14:G14)</f>
         <v>8</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="10" t="n">
         <f aca="false">RANK(H14,$H$5:$H$14)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
